--- a/Results/Open Models/Consistency/consistency_Ministral_3B_Instruct.xlsx
+++ b/Results/Open Models/Consistency/consistency_Ministral_3B_Instruct.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filow\Desktop\Repository\LLM-EVAL-Education\Results\Open Models\Consistency\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4D26C1-FF15-48CA-B05D-6C4322D8EF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="16230" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10128" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10089" uniqueCount="395">
   <si>
     <t>RUN_EXAM</t>
   </si>
@@ -1200,15 +1206,12 @@
   <si>
     <t>E</t>
   </si>
-  <si>
-    <t>ND</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1267,17 +1270,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1315,7 +1326,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1349,6 +1360,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1383,9 +1395,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1558,11 +1571,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:EK251"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.26171875" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="12.47265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:141">
+    <row r="1" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1987,7 +2004,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:141">
+    <row r="2" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>141</v>
       </c>
@@ -2412,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:141">
+    <row r="3" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -2837,7 +2854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:141">
+    <row r="4" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>143</v>
       </c>
@@ -3262,7 +3279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:141">
+    <row r="5" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>144</v>
       </c>
@@ -3687,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:141">
+    <row r="6" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>145</v>
       </c>
@@ -4112,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:141">
+    <row r="7" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -4537,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:141">
+    <row r="8" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -4962,7 +4979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:141">
+    <row r="9" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -5387,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:141">
+    <row r="10" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>149</v>
       </c>
@@ -5812,7 +5829,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="11" spans="1:141">
+    <row r="11" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -6237,7 +6254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:141">
+    <row r="12" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -6662,7 +6679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:141">
+    <row r="13" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -7087,7 +7104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:141">
+    <row r="14" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>153</v>
       </c>
@@ -7512,7 +7529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:141">
+    <row r="15" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>154</v>
       </c>
@@ -7937,7 +7954,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="16" spans="1:141">
+    <row r="16" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -8362,7 +8379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:141">
+    <row r="17" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -8787,7 +8804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:141">
+    <row r="18" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -9212,7 +9229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:141">
+    <row r="19" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>158</v>
       </c>
@@ -9637,7 +9654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:141">
+    <row r="20" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>159</v>
       </c>
@@ -10062,7 +10079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:141">
+    <row r="21" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -10487,7 +10504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:141">
+    <row r="22" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>161</v>
       </c>
@@ -10912,7 +10929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:141">
+    <row r="23" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>162</v>
       </c>
@@ -11337,7 +11354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:141">
+    <row r="24" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>163</v>
       </c>
@@ -11762,7 +11779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:141">
+    <row r="25" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>164</v>
       </c>
@@ -12187,7 +12204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:141">
+    <row r="26" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>165</v>
       </c>
@@ -12612,7 +12629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:141">
+    <row r="27" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>166</v>
       </c>
@@ -13037,7 +13054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:141">
+    <row r="28" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>167</v>
       </c>
@@ -13462,7 +13479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:141">
+    <row r="29" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>168</v>
       </c>
@@ -13887,7 +13904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:141">
+    <row r="30" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>169</v>
       </c>
@@ -14312,7 +14329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:141">
+    <row r="31" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>170</v>
       </c>
@@ -14737,7 +14754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:141">
+    <row r="32" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>171</v>
       </c>
@@ -15162,7 +15179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:141">
+    <row r="33" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>172</v>
       </c>
@@ -15587,7 +15604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:141">
+    <row r="34" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>173</v>
       </c>
@@ -16012,7 +16029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:141">
+    <row r="35" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -16437,7 +16454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:141">
+    <row r="36" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>175</v>
       </c>
@@ -16862,7 +16879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:141">
+    <row r="37" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>176</v>
       </c>
@@ -17287,7 +17304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:141">
+    <row r="38" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>177</v>
       </c>
@@ -17712,7 +17729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:141">
+    <row r="39" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>178</v>
       </c>
@@ -18137,7 +18154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:141">
+    <row r="40" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>179</v>
       </c>
@@ -18562,7 +18579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:141">
+    <row r="41" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>180</v>
       </c>
@@ -18987,7 +19004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:141">
+    <row r="42" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>181</v>
       </c>
@@ -19412,7 +19429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:141">
+    <row r="43" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -19837,7 +19854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:141">
+    <row r="44" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -20262,7 +20279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:141">
+    <row r="45" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>184</v>
       </c>
@@ -20687,7 +20704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:141">
+    <row r="46" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>185</v>
       </c>
@@ -21112,7 +21129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:141">
+    <row r="47" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>186</v>
       </c>
@@ -21537,7 +21554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:141">
+    <row r="48" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -21962,7 +21979,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="49" spans="1:141">
+    <row r="49" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>188</v>
       </c>
@@ -22387,7 +22404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:141">
+    <row r="50" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>189</v>
       </c>
@@ -22812,7 +22829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:141">
+    <row r="51" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>190</v>
       </c>
@@ -23237,7 +23254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:141">
+    <row r="52" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>191</v>
       </c>
@@ -23662,7 +23679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:141">
+    <row r="53" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>192</v>
       </c>
@@ -24087,7 +24104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:141">
+    <row r="54" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>193</v>
       </c>
@@ -24512,7 +24529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:141">
+    <row r="55" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>194</v>
       </c>
@@ -24937,7 +24954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:141">
+    <row r="56" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>195</v>
       </c>
@@ -25362,7 +25379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:141">
+    <row r="57" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>196</v>
       </c>
@@ -25787,7 +25804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:141">
+    <row r="58" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -26212,7 +26229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:141">
+    <row r="59" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>198</v>
       </c>
@@ -26637,7 +26654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:141">
+    <row r="60" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -27062,7 +27079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:141">
+    <row r="61" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>200</v>
       </c>
@@ -27487,7 +27504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:141">
+    <row r="62" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>201</v>
       </c>
@@ -27912,7 +27929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:141">
+    <row r="63" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>202</v>
       </c>
@@ -28337,7 +28354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:141">
+    <row r="64" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>203</v>
       </c>
@@ -28762,7 +28779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:141">
+    <row r="65" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>204</v>
       </c>
@@ -29187,7 +29204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:141">
+    <row r="66" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>205</v>
       </c>
@@ -29612,7 +29629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:141">
+    <row r="67" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>206</v>
       </c>
@@ -30037,7 +30054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:141">
+    <row r="68" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>207</v>
       </c>
@@ -30462,7 +30479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:141">
+    <row r="69" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>208</v>
       </c>
@@ -30887,7 +30904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:141">
+    <row r="70" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>209</v>
       </c>
@@ -31312,7 +31329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:141">
+    <row r="71" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>210</v>
       </c>
@@ -31737,7 +31754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:141">
+    <row r="72" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -32162,7 +32179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:141">
+    <row r="73" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>212</v>
       </c>
@@ -32587,7 +32604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:141">
+    <row r="74" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>213</v>
       </c>
@@ -33012,7 +33029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:141">
+    <row r="75" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>214</v>
       </c>
@@ -33437,7 +33454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:141">
+    <row r="76" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>215</v>
       </c>
@@ -33862,7 +33879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:141">
+    <row r="77" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>216</v>
       </c>
@@ -34287,7 +34304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:141">
+    <row r="78" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>217</v>
       </c>
@@ -34712,7 +34729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:141">
+    <row r="79" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>218</v>
       </c>
@@ -35137,7 +35154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:141">
+    <row r="80" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>219</v>
       </c>
@@ -35562,7 +35579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:141">
+    <row r="81" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>220</v>
       </c>
@@ -35987,7 +36004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:141">
+    <row r="82" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>221</v>
       </c>
@@ -36412,7 +36429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:141">
+    <row r="83" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>222</v>
       </c>
@@ -36837,7 +36854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:141">
+    <row r="84" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>223</v>
       </c>
@@ -37262,7 +37279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:141">
+    <row r="85" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>224</v>
       </c>
@@ -37687,7 +37704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:141">
+    <row r="86" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>225</v>
       </c>
@@ -38112,7 +38129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:141">
+    <row r="87" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>226</v>
       </c>
@@ -38537,7 +38554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:141">
+    <row r="88" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>227</v>
       </c>
@@ -38962,7 +38979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:141">
+    <row r="89" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>228</v>
       </c>
@@ -39387,7 +39404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:141">
+    <row r="90" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>229</v>
       </c>
@@ -39812,7 +39829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:141">
+    <row r="91" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>230</v>
       </c>
@@ -40237,7 +40254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:141">
+    <row r="92" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>231</v>
       </c>
@@ -40662,7 +40679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:141">
+    <row r="93" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>232</v>
       </c>
@@ -41087,7 +41104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:141">
+    <row r="94" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>233</v>
       </c>
@@ -41512,7 +41529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:141">
+    <row r="95" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>234</v>
       </c>
@@ -41937,7 +41954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:141">
+    <row r="96" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>235</v>
       </c>
@@ -42362,7 +42379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:141">
+    <row r="97" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>236</v>
       </c>
@@ -42787,7 +42804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:141">
+    <row r="98" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>237</v>
       </c>
@@ -43212,7 +43229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:141">
+    <row r="99" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>238</v>
       </c>
@@ -43637,7 +43654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:141">
+    <row r="100" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>239</v>
       </c>
@@ -44062,7 +44079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:141">
+    <row r="101" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>240</v>
       </c>
@@ -44487,7 +44504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:141">
+    <row r="102" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>241</v>
       </c>
@@ -44912,7 +44929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:141">
+    <row r="103" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>242</v>
       </c>
@@ -45337,7 +45354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:141">
+    <row r="104" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>243</v>
       </c>
@@ -45762,7 +45779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:141">
+    <row r="105" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>244</v>
       </c>
@@ -46187,7 +46204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:141">
+    <row r="106" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>245</v>
       </c>
@@ -46612,7 +46629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:141">
+    <row r="107" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>246</v>
       </c>
@@ -47037,7 +47054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:141">
+    <row r="108" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>247</v>
       </c>
@@ -47462,7 +47479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:141">
+    <row r="109" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>248</v>
       </c>
@@ -47887,7 +47904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:141">
+    <row r="110" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>249</v>
       </c>
@@ -48312,7 +48329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:141">
+    <row r="111" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>250</v>
       </c>
@@ -48737,7 +48754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:141">
+    <row r="112" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>251</v>
       </c>
@@ -49162,7 +49179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:141">
+    <row r="113" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>252</v>
       </c>
@@ -49587,7 +49604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:141">
+    <row r="114" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>253</v>
       </c>
@@ -50012,7 +50029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:141">
+    <row r="115" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>254</v>
       </c>
@@ -50437,7 +50454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:141">
+    <row r="116" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>255</v>
       </c>
@@ -50862,7 +50879,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="117" spans="1:141">
+    <row r="117" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>256</v>
       </c>
@@ -51287,7 +51304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:141">
+    <row r="118" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>257</v>
       </c>
@@ -51712,7 +51729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:141">
+    <row r="119" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>258</v>
       </c>
@@ -52137,7 +52154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:141">
+    <row r="120" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>259</v>
       </c>
@@ -52562,7 +52579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:141">
+    <row r="121" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>260</v>
       </c>
@@ -52987,7 +53004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:141">
+    <row r="122" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>261</v>
       </c>
@@ -53412,7 +53429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:141">
+    <row r="123" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>262</v>
       </c>
@@ -53837,7 +53854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:141">
+    <row r="124" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -54262,7 +54279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:141">
+    <row r="125" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>264</v>
       </c>
@@ -54687,7 +54704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:141">
+    <row r="126" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>265</v>
       </c>
@@ -55112,7 +55129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:141">
+    <row r="127" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>266</v>
       </c>
@@ -55537,7 +55554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:141">
+    <row r="128" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -55962,7 +55979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:141">
+    <row r="129" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>268</v>
       </c>
@@ -56387,7 +56404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:141">
+    <row r="130" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>269</v>
       </c>
@@ -56812,7 +56829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:141">
+    <row r="131" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>270</v>
       </c>
@@ -57237,7 +57254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:141">
+    <row r="132" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>271</v>
       </c>
@@ -57662,7 +57679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:141">
+    <row r="133" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>272</v>
       </c>
@@ -58087,7 +58104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:141">
+    <row r="134" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>273</v>
       </c>
@@ -58512,7 +58529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:141">
+    <row r="135" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>274</v>
       </c>
@@ -58937,7 +58954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:141">
+    <row r="136" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>275</v>
       </c>
@@ -59362,7 +59379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:141">
+    <row r="137" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>276</v>
       </c>
@@ -59787,7 +59804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:141">
+    <row r="138" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>277</v>
       </c>
@@ -60212,7 +60229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:141">
+    <row r="139" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>278</v>
       </c>
@@ -60637,7 +60654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:141">
+    <row r="140" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -61062,7 +61079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:141">
+    <row r="141" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -61487,7 +61504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:141">
+    <row r="142" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>281</v>
       </c>
@@ -61912,7 +61929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:141">
+    <row r="143" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>282</v>
       </c>
@@ -62337,7 +62354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:141">
+    <row r="144" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>283</v>
       </c>
@@ -62762,7 +62779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:141">
+    <row r="145" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>284</v>
       </c>
@@ -63187,7 +63204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:141">
+    <row r="146" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>285</v>
       </c>
@@ -63612,7 +63629,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="147" spans="1:141">
+    <row r="147" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>286</v>
       </c>
@@ -64037,7 +64054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:141">
+    <row r="148" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>287</v>
       </c>
@@ -64462,7 +64479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:141">
+    <row r="149" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>288</v>
       </c>
@@ -64887,7 +64904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:141">
+    <row r="150" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>289</v>
       </c>
@@ -65312,7 +65329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:141">
+    <row r="151" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>290</v>
       </c>
@@ -65737,7 +65754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:141">
+    <row r="152" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>291</v>
       </c>
@@ -66140,8 +66157,8 @@
       <c r="ED152">
         <v>1</v>
       </c>
-      <c r="EE152" t="s">
-        <v>395</v>
+      <c r="EE152">
+        <v>1</v>
       </c>
       <c r="EF152">
         <v>1</v>
@@ -66162,7 +66179,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="153" spans="1:141">
+    <row r="153" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>292</v>
       </c>
@@ -66565,8 +66582,8 @@
       <c r="ED153">
         <v>1</v>
       </c>
-      <c r="EE153" t="s">
-        <v>395</v>
+      <c r="EE153">
+        <v>1</v>
       </c>
       <c r="EF153">
         <v>1</v>
@@ -66587,7 +66604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:141">
+    <row r="154" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>293</v>
       </c>
@@ -66990,8 +67007,8 @@
       <c r="ED154">
         <v>1</v>
       </c>
-      <c r="EE154" t="s">
-        <v>395</v>
+      <c r="EE154">
+        <v>1</v>
       </c>
       <c r="EF154">
         <v>1</v>
@@ -67012,7 +67029,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="155" spans="1:141">
+    <row r="155" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>294</v>
       </c>
@@ -67437,7 +67454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:141">
+    <row r="156" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>295</v>
       </c>
@@ -67840,8 +67857,8 @@
       <c r="ED156">
         <v>1</v>
       </c>
-      <c r="EE156" t="s">
-        <v>395</v>
+      <c r="EE156">
+        <v>1</v>
       </c>
       <c r="EF156">
         <v>1</v>
@@ -67862,7 +67879,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="157" spans="1:141">
+    <row r="157" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>296</v>
       </c>
@@ -68265,8 +68282,8 @@
       <c r="ED157" t="s">
         <v>394</v>
       </c>
-      <c r="EE157" t="s">
-        <v>395</v>
+      <c r="EE157">
+        <v>1</v>
       </c>
       <c r="EF157">
         <v>1</v>
@@ -68287,7 +68304,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="158" spans="1:141">
+    <row r="158" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>297</v>
       </c>
@@ -68690,8 +68707,8 @@
       <c r="ED158" t="s">
         <v>392</v>
       </c>
-      <c r="EE158" t="s">
-        <v>395</v>
+      <c r="EE158">
+        <v>1</v>
       </c>
       <c r="EF158" t="s">
         <v>394</v>
@@ -68712,7 +68729,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="159" spans="1:141">
+    <row r="159" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>298</v>
       </c>
@@ -69115,8 +69132,8 @@
       <c r="ED159" t="s">
         <v>392</v>
       </c>
-      <c r="EE159" t="s">
-        <v>395</v>
+      <c r="EE159">
+        <v>1</v>
       </c>
       <c r="EF159" t="s">
         <v>392</v>
@@ -69137,7 +69154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:141">
+    <row r="160" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>299</v>
       </c>
@@ -69540,8 +69557,8 @@
       <c r="ED160" t="s">
         <v>392</v>
       </c>
-      <c r="EE160" t="s">
-        <v>395</v>
+      <c r="EE160">
+        <v>1</v>
       </c>
       <c r="EF160" t="s">
         <v>394</v>
@@ -69562,7 +69579,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="161" spans="1:141">
+    <row r="161" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>300</v>
       </c>
@@ -69987,7 +70004,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="162" spans="1:141">
+    <row r="162" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>301</v>
       </c>
@@ -70390,8 +70407,8 @@
       <c r="ED162">
         <v>1</v>
       </c>
-      <c r="EE162" t="s">
-        <v>395</v>
+      <c r="EE162">
+        <v>1</v>
       </c>
       <c r="EF162">
         <v>1</v>
@@ -70412,7 +70429,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="163" spans="1:141">
+    <row r="163" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>302</v>
       </c>
@@ -70815,8 +70832,8 @@
       <c r="ED163">
         <v>1</v>
       </c>
-      <c r="EE163" t="s">
-        <v>395</v>
+      <c r="EE163">
+        <v>1</v>
       </c>
       <c r="EF163">
         <v>1</v>
@@ -70837,7 +70854,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="164" spans="1:141">
+    <row r="164" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>303</v>
       </c>
@@ -71240,8 +71257,8 @@
       <c r="ED164" t="s">
         <v>392</v>
       </c>
-      <c r="EE164" t="s">
-        <v>395</v>
+      <c r="EE164">
+        <v>1</v>
       </c>
       <c r="EF164">
         <v>1</v>
@@ -71262,7 +71279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:141">
+    <row r="165" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>304</v>
       </c>
@@ -71665,8 +71682,8 @@
       <c r="ED165">
         <v>1</v>
       </c>
-      <c r="EE165" t="s">
-        <v>395</v>
+      <c r="EE165">
+        <v>1</v>
       </c>
       <c r="EF165">
         <v>1</v>
@@ -71687,7 +71704,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="166" spans="1:141">
+    <row r="166" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>305</v>
       </c>
@@ -72112,7 +72129,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="167" spans="1:141">
+    <row r="167" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>306</v>
       </c>
@@ -72515,8 +72532,8 @@
       <c r="ED167" t="s">
         <v>392</v>
       </c>
-      <c r="EE167" t="s">
-        <v>395</v>
+      <c r="EE167">
+        <v>1</v>
       </c>
       <c r="EF167" t="s">
         <v>394</v>
@@ -72537,7 +72554,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="168" spans="1:141">
+    <row r="168" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>307</v>
       </c>
@@ -72940,8 +72957,8 @@
       <c r="ED168">
         <v>1</v>
       </c>
-      <c r="EE168" t="s">
-        <v>395</v>
+      <c r="EE168">
+        <v>1</v>
       </c>
       <c r="EF168" t="s">
         <v>394</v>
@@ -72962,7 +72979,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="169" spans="1:141">
+    <row r="169" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>308</v>
       </c>
@@ -73365,8 +73382,8 @@
       <c r="ED169">
         <v>1</v>
       </c>
-      <c r="EE169" t="s">
-        <v>395</v>
+      <c r="EE169">
+        <v>1</v>
       </c>
       <c r="EF169">
         <v>1</v>
@@ -73387,7 +73404,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="170" spans="1:141">
+    <row r="170" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>309</v>
       </c>
@@ -73812,7 +73829,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="171" spans="1:141">
+    <row r="171" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>310</v>
       </c>
@@ -74215,8 +74232,8 @@
       <c r="ED171">
         <v>1</v>
       </c>
-      <c r="EE171" t="s">
-        <v>395</v>
+      <c r="EE171">
+        <v>1</v>
       </c>
       <c r="EF171">
         <v>1</v>
@@ -74237,7 +74254,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="172" spans="1:141">
+    <row r="172" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>311</v>
       </c>
@@ -74640,8 +74657,8 @@
       <c r="ED172">
         <v>1</v>
       </c>
-      <c r="EE172" t="s">
-        <v>395</v>
+      <c r="EE172">
+        <v>1</v>
       </c>
       <c r="EF172">
         <v>1</v>
@@ -74662,7 +74679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:141">
+    <row r="173" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>312</v>
       </c>
@@ -75087,7 +75104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:141">
+    <row r="174" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>313</v>
       </c>
@@ -75490,8 +75507,8 @@
       <c r="ED174">
         <v>1</v>
       </c>
-      <c r="EE174" t="s">
-        <v>395</v>
+      <c r="EE174">
+        <v>1</v>
       </c>
       <c r="EF174">
         <v>1</v>
@@ -75512,7 +75529,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="175" spans="1:141">
+    <row r="175" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>314</v>
       </c>
@@ -75915,8 +75932,8 @@
       <c r="ED175">
         <v>1</v>
       </c>
-      <c r="EE175" t="s">
-        <v>395</v>
+      <c r="EE175">
+        <v>1</v>
       </c>
       <c r="EF175">
         <v>1</v>
@@ -75937,7 +75954,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="176" spans="1:141">
+    <row r="176" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>315</v>
       </c>
@@ -76340,8 +76357,8 @@
       <c r="ED176">
         <v>1</v>
       </c>
-      <c r="EE176" t="s">
-        <v>395</v>
+      <c r="EE176">
+        <v>1</v>
       </c>
       <c r="EF176">
         <v>1</v>
@@ -76362,7 +76379,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="177" spans="1:141">
+    <row r="177" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>316</v>
       </c>
@@ -76765,8 +76782,8 @@
       <c r="ED177">
         <v>1</v>
       </c>
-      <c r="EE177" t="s">
-        <v>395</v>
+      <c r="EE177">
+        <v>1</v>
       </c>
       <c r="EF177">
         <v>1</v>
@@ -76787,7 +76804,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="1:141">
+    <row r="178" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>317</v>
       </c>
@@ -77190,8 +77207,8 @@
       <c r="ED178">
         <v>1</v>
       </c>
-      <c r="EE178" t="s">
-        <v>395</v>
+      <c r="EE178">
+        <v>1</v>
       </c>
       <c r="EF178">
         <v>1</v>
@@ -77212,7 +77229,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="179" spans="1:141">
+    <row r="179" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>318</v>
       </c>
@@ -77615,8 +77632,8 @@
       <c r="ED179">
         <v>1</v>
       </c>
-      <c r="EE179" t="s">
-        <v>395</v>
+      <c r="EE179">
+        <v>1</v>
       </c>
       <c r="EF179">
         <v>1</v>
@@ -77637,7 +77654,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="180" spans="1:141">
+    <row r="180" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>319</v>
       </c>
@@ -78040,8 +78057,8 @@
       <c r="ED180" t="s">
         <v>392</v>
       </c>
-      <c r="EE180" t="s">
-        <v>395</v>
+      <c r="EE180">
+        <v>1</v>
       </c>
       <c r="EF180">
         <v>1</v>
@@ -78062,7 +78079,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="181" spans="1:141">
+    <row r="181" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
         <v>320</v>
       </c>
@@ -78465,8 +78482,8 @@
       <c r="ED181">
         <v>1</v>
       </c>
-      <c r="EE181" t="s">
-        <v>395</v>
+      <c r="EE181">
+        <v>1</v>
       </c>
       <c r="EF181">
         <v>1</v>
@@ -78487,7 +78504,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="182" spans="1:141">
+    <row r="182" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" t="s">
         <v>321</v>
       </c>
@@ -78890,8 +78907,8 @@
       <c r="ED182" t="s">
         <v>394</v>
       </c>
-      <c r="EE182" t="s">
-        <v>395</v>
+      <c r="EE182">
+        <v>1</v>
       </c>
       <c r="EF182" t="s">
         <v>392</v>
@@ -78912,7 +78929,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="183" spans="1:141">
+    <row r="183" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>322</v>
       </c>
@@ -79315,8 +79332,8 @@
       <c r="ED183" t="s">
         <v>392</v>
       </c>
-      <c r="EE183" t="s">
-        <v>395</v>
+      <c r="EE183">
+        <v>1</v>
       </c>
       <c r="EF183">
         <v>1</v>
@@ -79337,7 +79354,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="184" spans="1:141">
+    <row r="184" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>323</v>
       </c>
@@ -79740,8 +79757,8 @@
       <c r="ED184">
         <v>1</v>
       </c>
-      <c r="EE184" t="s">
-        <v>395</v>
+      <c r="EE184">
+        <v>1</v>
       </c>
       <c r="EF184">
         <v>1</v>
@@ -79762,7 +79779,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="185" spans="1:141">
+    <row r="185" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>324</v>
       </c>
@@ -80165,8 +80182,8 @@
       <c r="ED185">
         <v>1</v>
       </c>
-      <c r="EE185" t="s">
-        <v>395</v>
+      <c r="EE185">
+        <v>1</v>
       </c>
       <c r="EF185">
         <v>1</v>
@@ -80187,7 +80204,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="186" spans="1:141">
+    <row r="186" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>325</v>
       </c>
@@ -80590,8 +80607,8 @@
       <c r="ED186">
         <v>1</v>
       </c>
-      <c r="EE186" t="s">
-        <v>395</v>
+      <c r="EE186">
+        <v>1</v>
       </c>
       <c r="EF186">
         <v>1</v>
@@ -80612,7 +80629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:141">
+    <row r="187" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>326</v>
       </c>
@@ -81015,8 +81032,8 @@
       <c r="ED187">
         <v>1</v>
       </c>
-      <c r="EE187" t="s">
-        <v>395</v>
+      <c r="EE187">
+        <v>1</v>
       </c>
       <c r="EF187">
         <v>1</v>
@@ -81037,7 +81054,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="188" spans="1:141">
+    <row r="188" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>327</v>
       </c>
@@ -81440,8 +81457,8 @@
       <c r="ED188">
         <v>1</v>
       </c>
-      <c r="EE188" t="s">
-        <v>395</v>
+      <c r="EE188">
+        <v>1</v>
       </c>
       <c r="EF188" t="s">
         <v>394</v>
@@ -81462,7 +81479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:141">
+    <row r="189" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
         <v>328</v>
       </c>
@@ -81887,7 +81904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:141">
+    <row r="190" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>329</v>
       </c>
@@ -82290,8 +82307,8 @@
       <c r="ED190">
         <v>1</v>
       </c>
-      <c r="EE190" t="s">
-        <v>395</v>
+      <c r="EE190">
+        <v>1</v>
       </c>
       <c r="EF190" t="s">
         <v>394</v>
@@ -82312,7 +82329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:141">
+    <row r="191" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>330</v>
       </c>
@@ -82737,7 +82754,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="192" spans="1:141">
+    <row r="192" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
         <v>331</v>
       </c>
@@ -83140,8 +83157,8 @@
       <c r="ED192" t="s">
         <v>394</v>
       </c>
-      <c r="EE192" t="s">
-        <v>395</v>
+      <c r="EE192">
+        <v>1</v>
       </c>
       <c r="EF192">
         <v>1</v>
@@ -83162,7 +83179,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="193" spans="1:141">
+    <row r="193" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>332</v>
       </c>
@@ -83565,8 +83582,8 @@
       <c r="ED193" t="s">
         <v>392</v>
       </c>
-      <c r="EE193" t="s">
-        <v>395</v>
+      <c r="EE193">
+        <v>1</v>
       </c>
       <c r="EF193">
         <v>1</v>
@@ -83587,7 +83604,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="194" spans="1:141">
+    <row r="194" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>333</v>
       </c>
@@ -84012,7 +84029,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="195" spans="1:141">
+    <row r="195" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>334</v>
       </c>
@@ -84415,8 +84432,8 @@
       <c r="ED195">
         <v>1</v>
       </c>
-      <c r="EE195" t="s">
-        <v>395</v>
+      <c r="EE195">
+        <v>1</v>
       </c>
       <c r="EF195">
         <v>1</v>
@@ -84437,7 +84454,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="196" spans="1:141">
+    <row r="196" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>335</v>
       </c>
@@ -84862,7 +84879,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:141">
+    <row r="197" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>336</v>
       </c>
@@ -85265,8 +85282,8 @@
       <c r="ED197">
         <v>1</v>
       </c>
-      <c r="EE197" t="s">
-        <v>395</v>
+      <c r="EE197">
+        <v>1</v>
       </c>
       <c r="EF197">
         <v>1</v>
@@ -85287,7 +85304,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:141">
+    <row r="198" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>337</v>
       </c>
@@ -85690,8 +85707,8 @@
       <c r="ED198" t="s">
         <v>392</v>
       </c>
-      <c r="EE198" t="s">
-        <v>395</v>
+      <c r="EE198">
+        <v>1</v>
       </c>
       <c r="EF198">
         <v>1</v>
@@ -85712,7 +85729,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="199" spans="1:141">
+    <row r="199" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>338</v>
       </c>
@@ -86115,8 +86132,8 @@
       <c r="ED199">
         <v>1</v>
       </c>
-      <c r="EE199" t="s">
-        <v>395</v>
+      <c r="EE199">
+        <v>1</v>
       </c>
       <c r="EF199">
         <v>1</v>
@@ -86137,7 +86154,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="200" spans="1:141">
+    <row r="200" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>339</v>
       </c>
@@ -86562,7 +86579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:141">
+    <row r="201" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>340</v>
       </c>
@@ -86987,7 +87004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:141">
+    <row r="202" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>341</v>
       </c>
@@ -87412,7 +87429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:141">
+    <row r="203" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>342</v>
       </c>
@@ -87837,7 +87854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:141">
+    <row r="204" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>343</v>
       </c>
@@ -88262,7 +88279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:141">
+    <row r="205" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
         <v>344</v>
       </c>
@@ -88687,7 +88704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:141">
+    <row r="206" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
         <v>345</v>
       </c>
@@ -89112,7 +89129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:141">
+    <row r="207" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
         <v>346</v>
       </c>
@@ -89537,7 +89554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:141">
+    <row r="208" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>347</v>
       </c>
@@ -89962,7 +89979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:141">
+    <row r="209" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" t="s">
         <v>348</v>
       </c>
@@ -90387,7 +90404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:141">
+    <row r="210" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
         <v>349</v>
       </c>
@@ -90812,7 +90829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:141">
+    <row r="211" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>350</v>
       </c>
@@ -91237,7 +91254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:141">
+    <row r="212" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>351</v>
       </c>
@@ -91662,7 +91679,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="213" spans="1:141">
+    <row r="213" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>352</v>
       </c>
@@ -92087,7 +92104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:141">
+    <row r="214" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
         <v>353</v>
       </c>
@@ -92512,7 +92529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:141">
+    <row r="215" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
         <v>354</v>
       </c>
@@ -92937,7 +92954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:141">
+    <row r="216" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
         <v>355</v>
       </c>
@@ -93362,7 +93379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:141">
+    <row r="217" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
         <v>356</v>
       </c>
@@ -93787,7 +93804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:141">
+    <row r="218" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
         <v>357</v>
       </c>
@@ -94212,7 +94229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:141">
+    <row r="219" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" t="s">
         <v>358</v>
       </c>
@@ -94637,7 +94654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:141">
+    <row r="220" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
         <v>359</v>
       </c>
@@ -95062,7 +95079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:141">
+    <row r="221" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
         <v>360</v>
       </c>
@@ -95487,7 +95504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:141">
+    <row r="222" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
         <v>361</v>
       </c>
@@ -95912,7 +95929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:141">
+    <row r="223" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" t="s">
         <v>362</v>
       </c>
@@ -96337,7 +96354,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="224" spans="1:141">
+    <row r="224" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
         <v>363</v>
       </c>
@@ -96762,7 +96779,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="225" spans="1:141">
+    <row r="225" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
         <v>364</v>
       </c>
@@ -97187,7 +97204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:141">
+    <row r="226" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
         <v>365</v>
       </c>
@@ -97612,7 +97629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:141">
+    <row r="227" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
         <v>366</v>
       </c>
@@ -98037,7 +98054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:141">
+    <row r="228" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
         <v>367</v>
       </c>
@@ -98462,7 +98479,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="229" spans="1:141">
+    <row r="229" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" t="s">
         <v>368</v>
       </c>
@@ -98887,7 +98904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:141">
+    <row r="230" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
         <v>369</v>
       </c>
@@ -99312,7 +99329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:141">
+    <row r="231" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
         <v>370</v>
       </c>
@@ -99737,7 +99754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:141">
+    <row r="232" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" t="s">
         <v>371</v>
       </c>
@@ -100162,7 +100179,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="233" spans="1:141">
+    <row r="233" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
         <v>372</v>
       </c>
@@ -100587,7 +100604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:141">
+    <row r="234" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" t="s">
         <v>373</v>
       </c>
@@ -101012,7 +101029,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="235" spans="1:141">
+    <row r="235" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
         <v>374</v>
       </c>
@@ -101437,7 +101454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:141">
+    <row r="236" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" t="s">
         <v>375</v>
       </c>
@@ -101862,7 +101879,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="237" spans="1:141">
+    <row r="237" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" t="s">
         <v>376</v>
       </c>
@@ -102287,7 +102304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:141">
+    <row r="238" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" t="s">
         <v>377</v>
       </c>
@@ -102712,7 +102729,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="239" spans="1:141">
+    <row r="239" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
         <v>378</v>
       </c>
@@ -103137,7 +103154,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="240" spans="1:141">
+    <row r="240" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" t="s">
         <v>379</v>
       </c>
@@ -103562,7 +103579,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="241" spans="1:141">
+    <row r="241" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" t="s">
         <v>380</v>
       </c>
@@ -103987,7 +104004,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="242" spans="1:141">
+    <row r="242" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" t="s">
         <v>381</v>
       </c>
@@ -104412,7 +104429,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="243" spans="1:141">
+    <row r="243" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" t="s">
         <v>382</v>
       </c>
@@ -104837,7 +104854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:141">
+    <row r="244" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" t="s">
         <v>383</v>
       </c>
@@ -105262,7 +105279,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="245" spans="1:141">
+    <row r="245" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
         <v>384</v>
       </c>
@@ -105687,7 +105704,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="246" spans="1:141">
+    <row r="246" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" t="s">
         <v>385</v>
       </c>
@@ -106112,7 +106129,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="247" spans="1:141">
+    <row r="247" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
         <v>386</v>
       </c>
@@ -106537,7 +106554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:141">
+    <row r="248" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" t="s">
         <v>387</v>
       </c>
@@ -106962,7 +106979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:141">
+    <row r="249" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" t="s">
         <v>388</v>
       </c>
@@ -107387,7 +107404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:141">
+    <row r="250" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" t="s">
         <v>389</v>
       </c>
@@ -107812,7 +107829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:141">
+    <row r="251" spans="1:141" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" t="s">
         <v>390</v>
       </c>
